--- a/data/trans_orig/IP3103-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP3103-Habitat-trans_orig.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3371</t>
+          <t>2821</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2801</t>
+          <t>3123</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5823</t>
+          <t>6028</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15720</t>
+          <t>15667</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5735</t>
+          <t>5471</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16336</t>
+          <t>15578</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13702</t>
+          <t>13772</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27255</t>
+          <t>27333</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,06%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>58351</t>
+          <t>58091</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>77111</t>
+          <t>76471</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>60273</t>
+          <t>59760</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>79454</t>
+          <t>78903</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>124029</t>
+          <t>123845</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>151527</t>
+          <t>150399</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>55,35%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41230</t>
+          <t>41571</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59280</t>
+          <t>59630</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51600</t>
+          <t>52174</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70778</t>
+          <t>71490</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>50,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>97602</t>
+          <t>97760</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>124000</t>
+          <t>124059</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>45,66%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>614</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5815</t>
+          <t>5404</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4365</t>
+          <t>3614</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>712</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6848</t>
+          <t>6950</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3218</t>
+          <t>4206</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7457</t>
+          <t>8071</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8095</t>
+          <t>8194</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9984</t>
+          <t>10102</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21670</t>
+          <t>21594</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15695</t>
+          <t>15712</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29082</t>
+          <t>29363</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>28442</t>
+          <t>28350</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>46114</t>
+          <t>45863</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,0%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>68864</t>
+          <t>67950</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>89508</t>
+          <t>88323</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>89754</t>
+          <t>88768</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>112320</t>
+          <t>112361</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>164030</t>
+          <t>162647</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>194824</t>
+          <t>193640</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>50,66%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69007</t>
+          <t>69276</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89863</t>
+          <t>89881</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56107</t>
+          <t>55626</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76828</t>
+          <t>76910</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>129700</t>
+          <t>132523</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>161580</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>42,27%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4414</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13031</t>
+          <t>13168</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4718</t>
+          <t>4673</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14296</t>
+          <t>13736</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10907</t>
+          <t>10236</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23235</t>
+          <t>22828</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -2096,54 +2096,54 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4763</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,73%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4591</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,6%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>447</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>4465</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10308</t>
+          <t>10928</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22607</t>
+          <t>21818</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9495</t>
+          <t>9252</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20410</t>
+          <t>20808</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22156</t>
+          <t>22701</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>38767</t>
+          <t>39615</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,94%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>57161</t>
+          <t>55893</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>73790</t>
+          <t>73709</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>70418</t>
+          <t>70231</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>89034</t>
+          <t>88539</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>131627</t>
+          <t>131280</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>157658</t>
+          <t>156537</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,03%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>28368</t>
+          <t>29212</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44097</t>
+          <t>45515</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30530</t>
+          <t>31106</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>47197</t>
+          <t>47641</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>64073</t>
+          <t>64093</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>86526</t>
+          <t>87154</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,87%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4862</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13644</t>
+          <t>14360</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2506</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10274</t>
+          <t>9635</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9095</t>
+          <t>9028</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19699</t>
+          <t>20691</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>5115</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>4744</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15562</t>
+          <t>15826</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>30932</t>
+          <t>31694</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>10038</t>
+          <t>9896</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>23171</t>
+          <t>21907</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>29838</t>
+          <t>29189</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>49873</t>
+          <t>50614</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>79707</t>
+          <t>80622</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>103829</t>
+          <t>103295</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>71946</t>
+          <t>71283</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>93968</t>
+          <t>92987</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>158811</t>
+          <t>156779</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>191753</t>
+          <t>189328</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>48,21%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>65596</t>
+          <t>65514</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>89269</t>
+          <t>89293</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>70765</t>
+          <t>70240</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>92502</t>
+          <t>93631</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>142110</t>
+          <t>141640</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>173218</t>
+          <t>174853</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,52%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3644</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12314</t>
+          <t>12624</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8835</t>
+          <t>8881</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>21047</t>
+          <t>21348</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>14399</t>
+          <t>14462</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>28825</t>
+          <t>29669</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>620</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5901</t>
+          <t>5577</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2560</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10390</t>
+          <t>10280</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3937</t>
+          <t>4037</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>13418</t>
+          <t>13233</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>52751</t>
+          <t>53326</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>78316</t>
+          <t>77989</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,82 +3588,82 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>8,37%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>12,24%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>60773</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>50314</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>74011</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>9,01%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>7,46%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>10,97%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>124941</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>108587</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>143025</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>9,52%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
           <t>8,28%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>12,29%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>60773</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>49029</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>72859</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>9,01%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>7,27%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>10,8%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>124941</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>108712</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>144281</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>9,52%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>8,29%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,9%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>281962</t>
+          <t>282065</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>323639</t>
+          <t>324004</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>311377</t>
+          <t>313409</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>354940</t>
+          <t>356244</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>604329</t>
+          <t>606171</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>664654</t>
+          <t>665452</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,73%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>222073</t>
+          <t>221236</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>261997</t>
+          <t>262685</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>226317</t>
+          <t>227530</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>267321</t>
+          <t>266189</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>463488</t>
+          <t>461574</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>522266</t>
+          <t>516325</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,36%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>19001</t>
+          <t>18218</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>34052</t>
+          <t>33478</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>20452</t>
+          <t>20003</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>38378</t>
+          <t>36769</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>43634</t>
+          <t>42960</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>65608</t>
+          <t>66553</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4107</t>
+          <t>3764</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4090</t>
+          <t>4156</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5054</t>
+          <t>4672</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18754</t>
+          <t>18210</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35993</t>
+          <t>34374</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25819</t>
+          <t>26210</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43232</t>
+          <t>42702</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48920</t>
+          <t>49459</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>71698</t>
+          <t>71723</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>45500</t>
+          <t>46989</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>64747</t>
+          <t>65159</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>41890</t>
+          <t>41028</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>60971</t>
+          <t>60510</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>93651</t>
+          <t>93761</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>121178</t>
+          <t>120506</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>43,83%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25473</t>
+          <t>25265</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40931</t>
+          <t>41516</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31276</t>
+          <t>31963</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49260</t>
+          <t>50002</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>60998</t>
+          <t>59893</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>85854</t>
+          <t>85736</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,18%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11558</t>
+          <t>11415</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25551</t>
+          <t>24513</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11146</t>
+          <t>11001</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25491</t>
+          <t>24031</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>25186</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>44760</t>
+          <t>44136</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,05%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>605</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5747</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4142</t>
+          <t>3632</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7193</t>
+          <t>6379</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24764</t>
+          <t>25212</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41460</t>
+          <t>42465</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25610</t>
+          <t>25472</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42993</t>
+          <t>44010</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>54191</t>
+          <t>53635</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>79813</t>
+          <t>78274</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>72926</t>
+          <t>73022</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>94899</t>
+          <t>94740</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>75998</t>
+          <t>75598</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>99519</t>
+          <t>99014</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>157077</t>
+          <t>155076</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>188468</t>
+          <t>186605</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>47,24%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43742</t>
+          <t>43562</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62840</t>
+          <t>62543</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44607</t>
+          <t>45516</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65517</t>
+          <t>66333</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>95867</t>
+          <t>94848</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>122732</t>
+          <t>124151</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,43%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12378</t>
+          <t>11905</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25192</t>
+          <t>24599</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20334</t>
+          <t>20202</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>36820</t>
+          <t>36336</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>36861</t>
+          <t>36581</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>56052</t>
+          <t>56304</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,25%</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4551</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4387</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12626</t>
+          <t>13180</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24922</t>
+          <t>25939</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12063</t>
+          <t>12238</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25319</t>
+          <t>25758</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28478</t>
+          <t>28720</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>46664</t>
+          <t>47138</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,22%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>66468</t>
+          <t>65901</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>84638</t>
+          <t>85548</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>70978</t>
+          <t>71077</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>91016</t>
+          <t>90586</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>143409</t>
+          <t>143481</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>170309</t>
+          <t>169678</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>58,39%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25790</t>
+          <t>24903</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40855</t>
+          <t>41898</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27156</t>
+          <t>26950</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>44464</t>
+          <t>43850</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>56835</t>
+          <t>57579</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>79707</t>
+          <t>80681</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,76%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9149</t>
+          <t>8972</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19287</t>
+          <t>19802</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8666</t>
+          <t>8930</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19883</t>
+          <t>19733</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>19807</t>
+          <t>20767</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>35436</t>
+          <t>36150</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,44%</t>
         </is>
       </c>
     </row>
@@ -6460,7 +6460,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3934</t>
+          <t>4075</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14907</t>
+          <t>15497</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>30495</t>
+          <t>31132</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>14285</t>
+          <t>14062</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>28907</t>
+          <t>28758</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>33845</t>
+          <t>33473</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>54047</t>
+          <t>54310</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,22%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>76099</t>
+          <t>76014</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>99095</t>
+          <t>99672</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>77000</t>
+          <t>78698</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>100798</t>
+          <t>102592</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>160260</t>
+          <t>160003</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>192570</t>
+          <t>194125</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,84%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>51523</t>
+          <t>49938</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>73450</t>
+          <t>72470</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>55793</t>
+          <t>55935</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>78235</t>
+          <t>77740</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>113202</t>
+          <t>111653</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>142581</t>
+          <t>143640</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,61%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12042</t>
+          <t>12416</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>26868</t>
+          <t>26375</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>9623</t>
+          <t>8793</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>22500</t>
+          <t>21610</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>24997</t>
+          <t>25472</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>44712</t>
+          <t>45751</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>658</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6305</t>
+          <t>6917</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7662</t>
+          <t>7449</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>2955</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11615</t>
+          <t>11759</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>83499</t>
+          <t>84233</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>114339</t>
+          <t>115132</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>92404</t>
+          <t>91062</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>122894</t>
+          <t>123881</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>184273</t>
+          <t>184710</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>227684</t>
+          <t>228155</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>282638</t>
+          <t>281009</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>324864</t>
+          <t>323176</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>286857</t>
+          <t>285578</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>329726</t>
+          <t>330491</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>580151</t>
+          <t>584463</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>641218</t>
+          <t>643905</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,97%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>162222</t>
+          <t>160986</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>200140</t>
+          <t>199349</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>178985</t>
+          <t>175618</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>217557</t>
+          <t>215916</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>350091</t>
+          <t>351629</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>404820</t>
+          <t>406204</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,26%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>55320</t>
+          <t>55659</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>80212</t>
+          <t>81283</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>61305</t>
+          <t>62312</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>87362</t>
+          <t>89686</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>123160</t>
+          <t>125655</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>161522</t>
+          <t>160081</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -8056,7 +8056,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>4935</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4748</t>
+          <t>5149</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6938</t>
+          <t>6860</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18731</t>
+          <t>19100</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4399</t>
+          <t>4432</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14874</t>
+          <t>14191</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13630</t>
+          <t>12853</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27345</t>
+          <t>28311</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,78%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44303</t>
+          <t>44231</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>62123</t>
+          <t>63129</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>40476</t>
+          <t>40433</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>60287</t>
+          <t>59673</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>91175</t>
+          <t>89945</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118391</t>
+          <t>117690</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>44,81%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30052</t>
+          <t>30327</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47790</t>
+          <t>47992</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37751</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57012</t>
+          <t>56991</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>73251</t>
+          <t>73550</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>98963</t>
+          <t>98857</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,64%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14562</t>
+          <t>14701</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28025</t>
+          <t>28634</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22599</t>
+          <t>23277</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>39615</t>
+          <t>39982</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>41991</t>
+          <t>41884</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>62352</t>
+          <t>63556</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>24,2%</t>
         </is>
       </c>
     </row>
@@ -8738,7 +8738,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3039</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8773,7 +8773,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3391</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22869</t>
+          <t>22768</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39858</t>
+          <t>39048</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26599</t>
+          <t>26210</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45454</t>
+          <t>44483</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>54717</t>
+          <t>53954</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>79075</t>
+          <t>78688</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,54%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>56255</t>
+          <t>55541</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>76640</t>
+          <t>76097</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49824</t>
+          <t>49581</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>70926</t>
+          <t>69987</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>111883</t>
+          <t>110844</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>140736</t>
+          <t>139542</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,65%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41322</t>
+          <t>41321</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59197</t>
+          <t>59786</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46338</t>
+          <t>45196</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66746</t>
+          <t>66539</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>93010</t>
+          <t>92111</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>120536</t>
+          <t>118923</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,53%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38511</t>
+          <t>37646</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>56217</t>
+          <t>56177</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48711</t>
+          <t>48732</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>69212</t>
+          <t>70749</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>92303</t>
+          <t>91571</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>119576</t>
+          <t>120164</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,84%</t>
         </is>
       </c>
     </row>
@@ -9385,7 +9385,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4339</t>
+          <t>4343</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9420,7 +9420,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3537</t>
+          <t>4006</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6266</t>
+          <t>5772</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9470,7 +9470,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7558</t>
+          <t>7823</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17673</t>
+          <t>17783</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5644</t>
+          <t>5588</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15990</t>
+          <t>15708</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15512</t>
+          <t>15327</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>30232</t>
+          <t>30384</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,97%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>50138</t>
+          <t>50307</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>68008</t>
+          <t>68089</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>56500</t>
+          <t>57242</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>76721</t>
+          <t>77132</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>111664</t>
+          <t>112079</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>139301</t>
+          <t>138698</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>45,51%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22930</t>
+          <t>22758</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39548</t>
+          <t>37829</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28271</t>
+          <t>28343</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46785</t>
+          <t>45075</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>54424</t>
+          <t>54809</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>78663</t>
+          <t>78730</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,83%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34709</t>
+          <t>34908</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>51967</t>
+          <t>51533</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>36181</t>
+          <t>36057</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>56201</t>
+          <t>54224</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>76664</t>
+          <t>76210</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>101859</t>
+          <t>101222</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,21%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>577</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5626</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10082,7 +10082,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3777</t>
+          <t>3586</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>720</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6451</t>
+          <t>6494</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12816</t>
+          <t>13173</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>29046</t>
+          <t>27625</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>12785</t>
+          <t>12709</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>27026</t>
+          <t>26352</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>29512</t>
+          <t>28637</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>49223</t>
+          <t>48715</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,78%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>53659</t>
+          <t>54657</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>77291</t>
+          <t>75814</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>61518</t>
+          <t>61855</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>85122</t>
+          <t>83607</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>121546</t>
+          <t>122993</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>153622</t>
+          <t>153279</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,23%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>45281</t>
+          <t>46130</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>66810</t>
+          <t>67351</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>41956</t>
+          <t>42646</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>63068</t>
+          <t>63038</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>93778</t>
+          <t>93931</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>124618</t>
+          <t>121100</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>31,78%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>39261</t>
+          <t>39040</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>59325</t>
+          <t>59779</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>35850</t>
+          <t>36406</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>55060</t>
+          <t>56236</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>79940</t>
+          <t>80905</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>109089</t>
+          <t>109885</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,84%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7764</t>
+          <t>7970</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7750</t>
+          <t>7758</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3478</t>
+          <t>3568</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>12655</t>
+          <t>12541</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10834,7 +10834,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>61481</t>
+          <t>61699</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>88394</t>
+          <t>88853</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>59195</t>
+          <t>58825</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>87397</t>
+          <t>86912</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>128712</t>
+          <t>127575</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>166873</t>
+          <t>165202</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,23%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>223376</t>
+          <t>221770</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>264388</t>
+          <t>263654</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>228659</t>
+          <t>228204</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>270044</t>
+          <t>271364</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>464806</t>
+          <t>464451</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>522829</t>
+          <t>523166</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,72%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>154788</t>
+          <t>155368</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>193295</t>
+          <t>194104</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>172585</t>
+          <t>173055</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>211685</t>
+          <t>209678</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>338515</t>
+          <t>340311</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>393568</t>
+          <t>393357</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,11%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>143423</t>
+          <t>142833</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>178662</t>
+          <t>178026</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>159248</t>
+          <t>161860</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>198444</t>
+          <t>199892</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>313279</t>
+          <t>315970</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>365024</t>
+          <t>367613</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,21%</t>
         </is>
       </c>
     </row>
